--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.34559948491519</v>
+        <v>9.643659916298718</v>
       </c>
       <c r="D2" t="n">
-        <v>56.59017115693143</v>
+        <v>9.195902813001357</v>
       </c>
       <c r="E2" t="n">
-        <v>6.520409972264581</v>
+        <v>1.059566620492994</v>
       </c>
       <c r="F2" t="n">
-        <v>5.444325762919281</v>
+        <v>0.8847029364743833</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.30477954038603</v>
+        <v>7.52452667531273</v>
       </c>
       <c r="D3" t="n">
-        <v>45.70151963109286</v>
+        <v>7.426496940052591</v>
       </c>
       <c r="E3" t="n">
-        <v>6.520409972264581</v>
+        <v>1.059566620492994</v>
       </c>
       <c r="F3" t="n">
-        <v>5.444325762919281</v>
+        <v>0.8847029364743833</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
